--- a/data/trans_dic/ProblemasDormirP33b-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,64</t>
+          <t>0,47; 3,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,64</t>
+          <t>1,37; 4,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,12</t>
+          <t>1,08; 3,03</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 10,51</t>
+          <t>4,27; 9,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 16,83</t>
+          <t>11,69; 16,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,37</t>
+          <t>8,63; 12,28</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 20,92</t>
+          <t>12,3; 20,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 26,05</t>
+          <t>18,72; 26,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,71; 22,43</t>
+          <t>16,56; 21,96</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 21,21</t>
+          <t>11,29; 21,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,86; 24,49</t>
+          <t>10,96; 24,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 21,64</t>
+          <t>12,89; 21,26</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,01</t>
+          <t>2,13; 6,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,11</t>
+          <t>3,06; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,81</t>
+          <t>3,55; 6,88</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,82</t>
+          <t>9,48; 16,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,8; 26,65</t>
+          <t>18,75; 26,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,49</t>
+          <t>15,12; 20,36</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,77; 19,27</t>
+          <t>12,95; 19,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,63; 26,07</t>
+          <t>9,13; 26,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,86; 21,27</t>
+          <t>11,54; 21,47</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 20,46</t>
+          <t>6,88; 20,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,14; 32,77</t>
+          <t>27,06; 32,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,13; 25,58</t>
+          <t>12,75; 25,67</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,64; 13,47</t>
+          <t>9,41; 13,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,21; 20,49</t>
+          <t>15,14; 20,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,81</t>
+          <t>13,35; 16,81</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario</t>
+          <t>Población con problemas para dormir a diario (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1553; 8212</t>
+          <t>1476; 9653</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3990; 13445</t>
+          <t>3966; 13999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6155; 18742</t>
+          <t>6481; 18187</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22124; 54498</t>
+          <t>22157; 50654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60418; 86673</t>
+          <t>60188; 86730</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86958; 127869</t>
+          <t>89161; 126888</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40236; 66104</t>
+          <t>38873; 64188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64317; 90949</t>
+          <t>65367; 91205</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111119; 149212</t>
+          <t>110125; 146054</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36369; 66302</t>
+          <t>35292; 66288</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51660; 116508</t>
+          <t>52140; 116377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102996; 170622</t>
+          <t>101611; 167580</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4383; 12535</t>
+          <t>3816; 12356</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7261; 20989</t>
+          <t>7931; 21359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14850; 29809</t>
+          <t>15518; 30085</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26347; 45346</t>
+          <t>25555; 45493</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48328; 68493</t>
+          <t>48209; 69076</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>80415; 107901</t>
+          <t>79623; 107250</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>79700; 120296</t>
+          <t>80829; 124611</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81767; 221374</t>
+          <t>77567; 223355</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160077; 313407</t>
+          <t>169981; 316427</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>58088; 190004</t>
+          <t>63881; 193121</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>194825; 235184</t>
+          <t>194238; 236270</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216172; 421135</t>
+          <t>209854; 422671</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>333670; 466160</t>
+          <t>325701; 467253</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>564511; 760768</t>
+          <t>562143; 762810</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>966335; 1205571</t>
+          <t>957431; 1205638</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProblemasDormirP33b-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProblemasDormirP33b-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,1</t>
+          <t>0,43; 2,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,83</t>
+          <t>1,28; 4,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,03</t>
+          <t>1,06; 2,85</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,77</t>
+          <t>4,17; 9,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 16,84</t>
+          <t>11,14; 16,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,28</t>
+          <t>8,36; 12,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 20,31</t>
+          <t>12,69; 20,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 26,12</t>
+          <t>19,29; 26,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,96</t>
+          <t>17,22; 22,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 21,21</t>
+          <t>11,45; 21,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 24,46</t>
+          <t>20,09; 27,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 21,26</t>
+          <t>16,97; 23,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,91</t>
+          <t>2,07; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,25</t>
+          <t>5,23; 9,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,88</t>
+          <t>4,14; 7,22</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,48; 16,87</t>
+          <t>9,65; 16,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,75; 26,87</t>
+          <t>19,3; 26,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,12; 20,36</t>
+          <t>15,38; 20,2</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,95; 19,96</t>
+          <t>12,97; 19,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 26,3</t>
+          <t>22,7; 28,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,54; 21,47</t>
+          <t>19,14; 23,42</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 20,79</t>
+          <t>16,48; 21,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,06; 32,92</t>
+          <t>26,15; 31,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,75; 25,67</t>
+          <t>22,34; 26,03</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,41; 13,51</t>
+          <t>11,83; 14,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,14; 20,55</t>
+          <t>19,75; 22,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,35; 16,81</t>
+          <t>16,13; 17,82</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11112</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1476; 9653</t>
+          <t>1375; 8715</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3966; 13999</t>
+          <t>4058; 12642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6481; 18187</t>
+          <t>6718; 18096</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>34865</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>72104</t>
+          <t>73659</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106045</t>
+          <t>108524</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22157; 50654</t>
+          <t>22102; 50490</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60188; 86730</t>
+          <t>60900; 87524</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89161; 126888</t>
+          <t>90012; 131248</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>80938</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128256</t>
+          <t>131902</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>38873; 64188</t>
+          <t>40095; 63459</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65367; 91205</t>
+          <t>68762; 93142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110125; 146054</t>
+          <t>115761; 151729</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>58307</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>89456</t>
+          <t>98915</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139924</t>
+          <t>157222</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35292; 66288</t>
+          <t>42707; 80867</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52140; 116377</t>
+          <t>84769; 115229</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101611; 167580</t>
+          <t>134910; 183542</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>24102</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3816; 12356</t>
+          <t>4248; 13285</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7931; 21359</t>
+          <t>11962; 22276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15518; 30085</t>
+          <t>18006; 31379</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>58074</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92401</t>
+          <t>94862</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25555; 45493</t>
+          <t>26135; 44711</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48209; 69076</t>
+          <t>50893; 71149</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79623; 107250</t>
+          <t>82211; 107949</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>116438</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>162789</t>
+          <t>198079</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261871</t>
+          <t>314517</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>80829; 124611</t>
+          <t>93309; 140824</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>77567; 223355</t>
+          <t>175251; 219431</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>169981; 316427</t>
+          <t>285581; 349364</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>135620</t>
+          <t>151714</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>215150</t>
+          <t>242028</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>350770</t>
+          <t>393743</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>63881; 193121</t>
+          <t>131502; 173494</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>194238; 236270</t>
+          <t>217423; 263960</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>209854; 422671</t>
+          <t>363982; 424086</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>457867</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>697294</t>
+          <t>778116</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1113009</t>
+          <t>1235984</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>325701; 467253</t>
+          <t>417781; 501711</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>562143; 762810</t>
+          <t>738160; 822248</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>957431; 1205638</t>
+          <t>1172707; 1295263</t>
         </is>
       </c>
     </row>
